--- a/data/trans_dic/P36B02_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36B02_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,69; 98,0</t>
+          <t>92,44; 97,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,99; 85,88</t>
+          <t>77,04; 86,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,39; 90,77</t>
+          <t>81,81; 90,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,75; 97,0</t>
+          <t>90,99; 96,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,74; 97,77</t>
+          <t>92,6; 97,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,19; 92,19</t>
+          <t>84,45; 92,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,27; 94,31</t>
+          <t>87,99; 94,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,27; 95,65</t>
+          <t>89,57; 95,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93,59; 97,26</t>
+          <t>93,63; 97,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,81; 88,0</t>
+          <t>82,11; 88,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,79</t>
+          <t>86,31; 91,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,85; 95,69</t>
+          <t>91,42; 95,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,68; 90,92</t>
+          <t>84,95; 90,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,71; 90,72</t>
+          <t>84,9; 90,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,54; 88,25</t>
+          <t>81,99; 88,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,14; 76,17</t>
+          <t>67,27; 76,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,96; 92,34</t>
+          <t>86,86; 92,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,43; 92,98</t>
+          <t>87,65; 93,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,13; 92,35</t>
+          <t>87,16; 92,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,66; 82,15</t>
+          <t>76,12; 82,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,91; 90,74</t>
+          <t>86,7; 90,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,39; 91,43</t>
+          <t>87,38; 91,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85,58; 89,81</t>
+          <t>85,58; 89,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,45; 78,19</t>
+          <t>72,59; 78,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,4; 97,04</t>
+          <t>91,35; 97,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,88; 97,58</t>
+          <t>93,22; 97,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,0; 98,2</t>
+          <t>93,9; 98,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,89; 98,41</t>
+          <t>94,35; 98,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,24; 98,38</t>
+          <t>94,44; 98,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,33; 97,29</t>
+          <t>92,17; 97,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,41; 99,41</t>
+          <t>96,47; 99,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,3; 95,29</t>
+          <t>90,58; 95,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,99; 97,3</t>
+          <t>93,87; 97,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,64; 96,9</t>
+          <t>93,44; 96,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95,96; 98,37</t>
+          <t>95,83; 98,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,29</t>
+          <t>92,89; 96,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,77; 96,07</t>
+          <t>90,63; 96,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,0; 98,4</t>
+          <t>94,17; 98,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,11; 91,89</t>
+          <t>85,42; 92,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,17; 95,52</t>
+          <t>86,26; 94,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,31; 98,24</t>
+          <t>94,48; 98,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,78; 98,25</t>
+          <t>94,72; 98,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,26; 95,7</t>
+          <t>90,17; 95,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,34; 95,08</t>
+          <t>89,97; 94,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,57; 96,73</t>
+          <t>93,45; 96,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,15; 97,86</t>
+          <t>95,22; 97,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88,95; 93,17</t>
+          <t>88,72; 93,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,62; 93,86</t>
+          <t>89,3; 93,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,8; 94,81</t>
+          <t>86,47; 94,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,17; 98,16</t>
+          <t>92,4; 98,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,37; 99,53</t>
+          <t>95,23; 99,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,17; 99,0</t>
+          <t>94,96; 99,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,76; 98,55</t>
+          <t>91,9; 98,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,58; 96,23</t>
+          <t>88,98; 96,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,56; 99,63</t>
+          <t>96,72; 99,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>94,23; 98,87</t>
+          <t>95,76; 99,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,92; 96,02</t>
+          <t>90,94; 96,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,92; 96,42</t>
+          <t>91,69; 96,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96,82; 99,39</t>
+          <t>96,93; 99,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,86; 98,66</t>
+          <t>96,21; 98,72</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,01; 96,49</t>
+          <t>91,06; 96,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,1; 97,12</t>
+          <t>90,71; 97,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,55; 90,1</t>
+          <t>81,18; 90,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,71; 91,07</t>
+          <t>83,51; 90,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,25; 96,77</t>
+          <t>91,37; 96,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92,61; 97,6</t>
+          <t>93,03; 97,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,14; 95,06</t>
+          <t>88,85; 95,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,78; 94,65</t>
+          <t>89,56; 94,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92,42; 96,24</t>
+          <t>92,14; 96,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93,08; 96,83</t>
+          <t>92,82; 96,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86,67; 91,89</t>
+          <t>86,06; 91,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>87,42; 92,29</t>
+          <t>87,54; 92,05</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>92,1; 96,18</t>
+          <t>92,4; 96,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,51; 95,57</t>
+          <t>91,51; 95,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,61; 94,03</t>
+          <t>89,43; 94,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,83; 92,75</t>
+          <t>87,23; 92,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,66; 94,05</t>
+          <t>89,63; 94,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,6; 95,36</t>
+          <t>91,56; 95,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3; 93,76</t>
+          <t>89,37; 93,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,71; 96,48</t>
+          <t>86,67; 90,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,81; 94,66</t>
+          <t>91,66; 94,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92,33; 94,96</t>
+          <t>92,39; 95,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90,23; 93,43</t>
+          <t>90,26; 93,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,85; 94,45</t>
+          <t>87,76; 91,22</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>90,49; 94,21</t>
+          <t>90,41; 94,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95,17; 98,08</t>
+          <t>95,28; 98,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,48; 98,17</t>
+          <t>95,33; 98,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,31; 94,59</t>
+          <t>80,55; 86,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>94,16; 96,96</t>
+          <t>94,29; 97,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,17; 97,8</t>
+          <t>95,4; 97,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,97; 98,23</t>
+          <t>96,05; 98,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,52; 88,74</t>
+          <t>84,52; 88,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>92,89; 95,36</t>
+          <t>92,95; 95,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95,75; 97,66</t>
+          <t>95,81; 97,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96,13; 97,88</t>
+          <t>96,2; 97,91</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>84,34; 92,05</t>
+          <t>83,41; 86,68</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,75</t>
+          <t>91,94; 93,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>92,29; 94,22</t>
+          <t>92,41; 94,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90,77; 92,78</t>
+          <t>90,76; 92,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86,42; 90,65</t>
+          <t>85,85; 88,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>93,47; 95,01</t>
+          <t>93,53; 95,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>93,27; 94,98</t>
+          <t>93,29; 94,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,22; 94,87</t>
+          <t>93,23; 94,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,53</t>
+          <t>87,98; 89,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92,91; 94,19</t>
+          <t>93,01; 94,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93,13; 94,38</t>
+          <t>93,17; 94,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92,33; 93,49</t>
+          <t>92,29; 93,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85,02; 89,71</t>
+          <t>87,37; 88,83</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295390</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>270490</t>
+          <t>293528</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>565879</t>
+          <t>594409</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>253063; 267538</t>
+          <t>252368; 267193</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>226907; 253110</t>
+          <t>227074; 254583</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>241161; 265680</t>
+          <t>239447; 266190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285763; 302090</t>
+          <t>290124; 307999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>241906; 255034</t>
+          <t>241543; 254923</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>241821; 264813</t>
+          <t>242571; 264923</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>251944; 272271</t>
+          <t>254024; 272333</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>261454; 277046</t>
+          <t>283111; 300519</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>499606; 519226</t>
+          <t>499835; 519321</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>476124; 512126</t>
+          <t>477838; 514938</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>503104; 533647</t>
+          <t>501817; 534008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>552081; 575171</t>
+          <t>580418; 605667</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368862</t>
+          <t>380580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>406280</t>
+          <t>434141</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>775142</t>
+          <t>814721</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>417545; 448305</t>
+          <t>418870; 447534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>428231; 458605</t>
+          <t>429214; 459723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>408908; 442547</t>
+          <t>411183; 442923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>342881; 394865</t>
+          <t>356951; 405139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>438212; 465325</t>
+          <t>437707; 465478</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>457910; 486999</t>
+          <t>459100; 487240</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>455760; 483090</t>
+          <t>455926; 483566</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>389648; 423028</t>
+          <t>415987; 451576</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>866471; 904703</t>
+          <t>864402; 905010</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>899450; 941128</t>
+          <t>899424; 941230</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>876806; 920130</t>
+          <t>876784; 919169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>748702; 808002</t>
+          <t>781935; 842027</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306965</t>
+          <t>305368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>325003</t>
+          <t>332016</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>631968</t>
+          <t>637385</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>291415; 309411</t>
+          <t>291263; 309576</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300969; 316196</t>
+          <t>302068; 316356</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298541; 311884</t>
+          <t>298227; 311949</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299907; 311028</t>
+          <t>298149; 309764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>316081; 329983</t>
+          <t>316772; 330000</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>314858; 331776</t>
+          <t>314330; 331169</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>324235; 334311</t>
+          <t>324445; 334286</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>315276; 332697</t>
+          <t>322816; 339672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>614951; 636598</t>
+          <t>614148; 636342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>622755; 644478</t>
+          <t>621417; 644084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>627469; 643242</t>
+          <t>626652; 643754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>620504; 640519</t>
+          <t>624550; 646512</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288964</t>
+          <t>340553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>382614</t>
+          <t>390134</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>671578</t>
+          <t>730687</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>325583; 344574</t>
+          <t>325080; 345327</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>351537; 367985</t>
+          <t>352168; 368310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>314891; 339945</t>
+          <t>316032; 340567</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>272456; 298553</t>
+          <t>321859; 353181</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>350312; 364906</t>
+          <t>350967; 364696</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>367782; 381238</t>
+          <t>367549; 381388</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>348785; 369771</t>
+          <t>348436; 369821</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>234718; 452308</t>
+          <t>379637; 399194</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>683208; 706217</t>
+          <t>682330; 706305</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>725034; 745747</t>
+          <t>725572; 745528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>672779; 704674</t>
+          <t>671042; 704890</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>485767; 739862</t>
+          <t>710024; 746814</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174765</t>
+          <t>200747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>202901</t>
+          <t>222282</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>377666</t>
+          <t>423028</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>176472; 192761</t>
+          <t>175799; 192755</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>195968; 208709</t>
+          <t>196468; 208557</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>201437; 210236</t>
+          <t>201154; 210246</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170108; 176951</t>
+          <t>195308; 203604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>190551; 204661</t>
+          <t>190840; 203779</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>194513; 211316</t>
+          <t>195394; 211344</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>211065; 217778</t>
+          <t>211415; 217767</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>196251; 205925</t>
+          <t>217207; 224720</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>373649; 394602</t>
+          <t>373737; 395086</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>397288; 416717</t>
+          <t>396291; 416236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>416142; 427181</t>
+          <t>416634; 427333</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>370995; 381831</t>
+          <t>416094; 426963</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236692</t>
+          <t>236302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>238127</t>
+          <t>243716</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>474818</t>
+          <t>480017</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>246452; 261294</t>
+          <t>246600; 261218</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>249603; 266079</t>
+          <t>248537; 265971</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>214574; 237082</t>
+          <t>213608; 236924</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>225700; 245559</t>
+          <t>226054; 245686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>253806; 269165</t>
+          <t>254152; 269239</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>258435; 272358</t>
+          <t>259590; 272401</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>243448; 259612</t>
+          <t>242652; 259647</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>230779; 243315</t>
+          <t>236204; 249285</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>507322; 528293</t>
+          <t>505832; 527848</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>514775; 535479</t>
+          <t>513317; 535252</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>464757; 492743</t>
+          <t>461511; 492196</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>460433; 486093</t>
+          <t>467876; 491953</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>562430</t>
+          <t>648977</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>781331</t>
+          <t>685985</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1343761</t>
+          <t>1334962</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>566429; 591534</t>
+          <t>568304; 592125</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>605656; 632559</t>
+          <t>605673; 631838</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>586593; 615562</t>
+          <t>585422; 615475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>542079; 579000</t>
+          <t>627817; 665194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>571237; 599172</t>
+          <t>571000; 598859</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>631853; 657815</t>
+          <t>631607; 658653</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>615447; 646235</t>
+          <t>615970; 645951</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>753375; 819355</t>
+          <t>669120; 701061</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1149570; 1185258</t>
+          <t>1147661; 1185759</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1248066; 1283558</t>
+          <t>1248858; 1286830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1212479; 1255593</t>
+          <t>1212966; 1253529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1309182; 1391831</t>
+          <t>1309091; 1360730</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>813405</t>
+          <t>666129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>621940</t>
+          <t>720879</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1435347</t>
+          <t>1387008</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>672269; 699875</t>
+          <t>671678; 699598</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>741498; 764132</t>
+          <t>742346; 764717</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>741647; 762561</t>
+          <t>740431; 761230</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>764469; 878458</t>
+          <t>642836; 689001</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>737773; 759673</t>
+          <t>738804; 760329</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>784093; 805713</t>
+          <t>785983; 806411</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>792881; 811523</t>
+          <t>793518; 811645</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>606608; 636900</t>
+          <t>702610; 737864</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1417921; 1455643</t>
+          <t>1418820; 1454943</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1534837; 1565423</t>
+          <t>1535768; 1565900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1540915; 1568916</t>
+          <t>1541919; 1569369</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1388631; 1515604</t>
+          <t>1359134; 1412363</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3047473</t>
+          <t>3079536</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3228685</t>
+          <t>3322683</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6276158</t>
+          <t>6402219</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3010865; 3070960</t>
+          <t>3011724; 3071974</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3161665; 3227948</t>
+          <t>3165996; 3224637</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3074831; 3142986</t>
+          <t>3074343; 3139692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2989897; 3136156</t>
+          <t>3032838; 3124665</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3157344; 3209454</t>
+          <t>3159450; 3214503</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3313344; 3374125</t>
+          <t>3314081; 3372541</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3301378; 3359736</t>
+          <t>3301831; 3356938</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3024967; 3314975</t>
+          <t>3286012; 3355599</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6182195; 6267216</t>
+          <t>6188622; 6266671</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6498776; 6586109</t>
+          <t>6501487; 6583665</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6397489; 6478012</t>
+          <t>6394732; 6479156</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6055024; 6388820</t>
+          <t>6349366; 6455660</t>
         </is>
       </c>
     </row>
